--- a/data/trans_camb/P1404-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1404-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,44</t>
+          <t>10,9</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,43</t>
+          <t>13,81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,76</t>
+          <t>12,73</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,77</t>
+          <t>4,72; 11,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 13,19</t>
+          <t>5,96; 13,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 16,33</t>
+          <t>7,45; 14,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 11,41</t>
+          <t>5,19; 11,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 12,64</t>
+          <t>5,46; 12,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,36; 17,87</t>
+          <t>10,67; 17,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,65</t>
+          <t>5,99; 10,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 12,03</t>
+          <t>6,88; 11,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,29; 16,32</t>
+          <t>10,3; 15,31</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,72; 92,62</t>
+          <t>29,49; 91,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,86; 102,57</t>
+          <t>36,13; 105,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,42; 126,09</t>
+          <t>46,53; 117,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,18; 68,23</t>
+          <t>26,3; 71,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,37; 75,18</t>
+          <t>27,92; 77,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,8; 107,14</t>
+          <t>54,06; 103,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,08; 70,04</t>
+          <t>34,17; 69,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,68; 78,02</t>
+          <t>39,19; 76,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,78; 105,75</t>
+          <t>58,3; 100,93</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,83</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>6,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,26</t>
+          <t>0,11; 3,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,17</t>
+          <t>0,97; 4,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,03</t>
+          <t>5,58; 9,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,01</t>
+          <t>-0,36; 3,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,38</t>
+          <t>0,89; 4,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 36,27</t>
+          <t>4,17; 7,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,72</t>
+          <t>0,22; 2,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,73</t>
+          <t>1,49; 3,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 23,1</t>
+          <t>5,42; 7,78</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113,57%</t>
+          <t>140,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>249,78%</t>
+          <t>106,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>183,21%</t>
+          <t>123,44%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 76,0</t>
+          <t>1,25; 73,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 94,13</t>
+          <t>16,09; 95,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,09; 176,82</t>
+          <t>89,5; 206,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 61,02</t>
+          <t>-5,38; 66,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,83; 91,3</t>
+          <t>13,93; 92,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,95; 831,07</t>
+          <t>65,15; 162,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 56,42</t>
+          <t>3,61; 54,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,62; 77,32</t>
+          <t>25,21; 81,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,31; 465,88</t>
+          <t>89,51; 165,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,84</t>
+          <t>7,07</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>7,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,19</t>
+          <t>7,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 6,08</t>
+          <t>-0,24; 6,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,1</t>
+          <t>0,47; 7,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,27</t>
+          <t>4,11; 9,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 2,46</t>
+          <t>-3,25; 2,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,83</t>
+          <t>-0,69; 4,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 10,47</t>
+          <t>4,83; 10,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,58</t>
+          <t>-0,86; 3,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,12</t>
+          <t>0,8; 5,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,19</t>
+          <t>5,33; 9,47</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146,61%</t>
+          <t>151,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>175,91%</t>
+          <t>181,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>159,91%</t>
+          <t>165,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 170,47</t>
+          <t>-5,43; 189,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 208,01</t>
+          <t>4,43; 201,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,06; 320,2</t>
+          <t>64,87; 296,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,3; 83,81</t>
+          <t>-58,07; 80,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,5; 171,42</t>
+          <t>-13,94; 158,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74,04; 367,52</t>
+          <t>75,36; 377,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 91,45</t>
+          <t>-17,04; 91,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,64; 136,5</t>
+          <t>12,69; 142,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85,55; 253,48</t>
+          <t>96,96; 276,01</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,55</t>
+          <t>6,48</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,44</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,08</t>
+          <t>6,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,89</t>
+          <t>2,08; 5,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,07</t>
+          <t>2,13; 4,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,41</t>
+          <t>4,86; 7,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,13</t>
+          <t>1,84; 5,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,67</t>
+          <t>1,48; 4,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 27,93</t>
+          <t>4,38; 7,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,56</t>
+          <t>2,52; 4,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,3</t>
+          <t>2,21; 4,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 17,81</t>
+          <t>5,13; 7,13</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>101,34%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,75; 65,5</t>
+          <t>24,18; 68,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,1; 68,04</t>
+          <t>24,7; 67,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,72; 98,93</t>
+          <t>57,94; 110,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,91; 54,13</t>
+          <t>15,91; 52,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,96; 49,65</t>
+          <t>12,79; 47,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,26; 270,62</t>
+          <t>38,42; 77,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,57; 52,96</t>
+          <t>26,03; 52,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,25; 50,06</t>
+          <t>23,33; 50,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>55,36; 195,78</t>
+          <t>53,07; 83,6</t>
         </is>
       </c>
     </row>
